--- a/data-manipulation-scripts/sheets-cleanup/sheets/DISCO EMBREAGEM 05_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/DISCO EMBREAGEM 05_02.xlsx
@@ -16,7 +16,7 @@
     <t>CÓD. BARRA</t>
   </si>
   <si>
-    <t>DESCRIÇÃO</t>
+    <t>DISCRIÇÃO</t>
   </si>
   <si>
     <t>QUANTIDADE</t>
@@ -28,121 +28,121 @@
     <t xml:space="preserve">  7895099123364</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMIRON TITAN FAN150 2005 A 2014/ FAN125 2009 039892</t>
+    <t>DISCO EMBREAGEM  IRON TITAN FAN150 2005 A 2014/ FAN125 2009 039892</t>
   </si>
   <si>
     <t>7895099123371</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMIRON CG FAN TITAN160 041441</t>
+    <t>DISCO EMBREAGEM  IRON CG FAN TITAN160 041441</t>
   </si>
   <si>
     <t>78983095182</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMCB300R/ XRE300 1151088</t>
+    <t>DISCO EMBREAGEM  CB300R/ XRE300 1151088</t>
   </si>
   <si>
     <t>7895099123333</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMIRON FAZER YS250/ XTZ LANDER250 09865</t>
+    <t>DISCO EMBREAGEM  IRON FAZER YS250/ XTZ LANDISCO EMBREAGEM   R250 09865</t>
   </si>
   <si>
     <t>7895099123302</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMIRON YBR125 2000 A 2008/ FACTOR125 2009 A 2016 014855</t>
+    <t>DISCO EMBREAGEM  IRON YBR125 2000 A 2008/ FACTOR125 2009 A 2016 014855</t>
   </si>
   <si>
     <t>6974288492199</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMBRAVIC FAZER250/ LANDER250 BMA33011</t>
+    <t>DISCO EMBREAGEM  BRAVIC FAZER250/ LANDISCO EMBREAGEM   R250 BMA33011</t>
   </si>
   <si>
     <t>7895797871161</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMCONTROLFLEX POP110I 2016</t>
+    <t>DISCO EMBREAGEM  CONTROLFLEX POP110I 2016</t>
   </si>
   <si>
     <t>7895099123357</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMIRON FAZER150 039890</t>
+    <t>DISCO EMBREAGEM  IRON FAZER150 039890</t>
   </si>
   <si>
     <t>7895099123296</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMIRON POP100 110I 039886</t>
+    <t>DISCO EMBREAGEM  IRON POP100 110I 039886</t>
   </si>
   <si>
     <t>7898558331546</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMWGK YES125 1018641</t>
+    <t>DISCO EMBREAGEM  WGK YES125 1018641</t>
   </si>
   <si>
     <t>7899248167667</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMGP YBR125 1102622</t>
+    <t>DISCO EMBREAGEM  GP YBR125 1102622</t>
   </si>
   <si>
     <t>7895099123005</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMIRON CBX250 TWISTER 14856</t>
+    <t>DISCO EMBREAGEM  IRON CBX250 TWISTER 14856</t>
   </si>
   <si>
     <t>7893986534194</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMPECA+ TRAXX JL50Q2/ SHINERAY WAVE110/ HUNTER125/ DAFRA ZIG50</t>
+    <t>DISCO EMBREAGEM  PECA+ TRAXX JL50Q2/ SHINERAY WAVE110/ HUNTER125/ DAFRA ZIG50</t>
   </si>
   <si>
     <t>7895099119329</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMIRON BIZ125 014839</t>
+    <t>DISCO EMBREAGEM  IRON BIZ125 014839</t>
   </si>
   <si>
     <t>070341173411</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMIRON TITAN150 KS/ES 351241</t>
+    <t>DISCO EMBREAGEM  IRON TITAN150 KS/ES 351241</t>
   </si>
   <si>
     <t>000010002223</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMRIIE CBX250 TWISTER/ TORNADO250 000222</t>
+    <t>DISCO EMBREAGEM  RIIE CBX250 TWISTER/ TORNADO250 000222</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMPANDAO SHINERAY50/ SUNDOWN HUNTER90</t>
+    <t>DISCO EMBREAGEM  PANDAO SHINERAY50/ SUNDOWN HUNTER90</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMRT SHINERAY50</t>
+    <t>DISCO EMBREAGEM  RT SHINERAY50</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMHONDA CG FAN TITAN150 160/ BROS150 160</t>
+    <t>DISCO EMBREAGEM  HONDA CG FAN TITAN150 160/ BROS150 160</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMHONDA CG TITAN FAN150</t>
+    <t>DISCO EMBREAGEM  HONDA CG TITAN FAN150</t>
   </si>
   <si>
     <t>1000007944009</t>
   </si>
   <si>
-    <t>DISCO EMBREAGEMRT FAZER250 794400</t>
+    <t>DISCO EMBREAGEM  RT FAZER250 794400</t>
   </si>
   <si>
     <t>6942234809391</t>
   </si>
   <si>
-    <t>DE BRAVIC POP110I BMA32601</t>
+    <t>DISCO EMBREAGEM    BRAVIC POP110I BMA32601</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
